--- a/docs/StructureDefinition-AdersA.xlsx
+++ b/docs/StructureDefinition-AdersA.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AdersA.xlsx
+++ b/docs/StructureDefinition-AdersA.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AdersA.xlsx
+++ b/docs/StructureDefinition-AdersA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2615" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2584" uniqueCount="239">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>AdersA.2ptdob</t>
+    <t>AdersA.pticnfull</t>
   </si>
   <si>
     <t>1</t>
@@ -257,487 +257,481 @@
 </t>
   </si>
   <si>
-    <t>2_ptDOB (-2)</t>
-  </si>
-  <si>
-    <t>AdersA.3ptsex</t>
-  </si>
-  <si>
-    <t>3_ptSex (-3)</t>
-  </si>
-  <si>
-    <t>AdersA.21death</t>
-  </si>
-  <si>
-    <t>21_Death (-21.6)</t>
-  </si>
-  <si>
-    <t>AdersA.21deathdt</t>
-  </si>
-  <si>
-    <t>21_DeathDt (-21.7)</t>
-  </si>
-  <si>
-    <t>AdersA.24ptraceaian</t>
-  </si>
-  <si>
-    <t>24_PtRace_AIAN (-24.1)</t>
-  </si>
-  <si>
-    <t>AdersA.24ptraceasian</t>
-  </si>
-  <si>
-    <t>24_PtRace_Asian (-24.2)</t>
-  </si>
-  <si>
-    <t>AdersA.24ptraceblkam</t>
-  </si>
-  <si>
-    <t>24_PtRace_BlkAM (-24.3)</t>
-  </si>
-  <si>
-    <t>AdersA.24ptracenhopi</t>
-  </si>
-  <si>
-    <t>24_PtRace_NH_OPI (-24.4)</t>
-  </si>
-  <si>
-    <t>AdersA.24ptracewhite</t>
-  </si>
-  <si>
-    <t>24_PtRace_White (-24.5)</t>
-  </si>
-  <si>
-    <t>AdersA.24ptraceunk</t>
-  </si>
-  <si>
-    <t>24_PtRace_Unk (-24.6)</t>
-  </si>
-  <si>
-    <t>AdersA.24ptraceother</t>
-  </si>
-  <si>
-    <t>24_PtRace_Other (-24.7)</t>
-  </si>
-  <si>
-    <t>AdersA.25ptethnicityhisplat</t>
-  </si>
-  <si>
-    <t>25_PtEthnicity_HispLat (-25.1)</t>
-  </si>
-  <si>
-    <t>AdersA.25ptethnicitynhl</t>
-  </si>
-  <si>
-    <t>25_PtEthnicity_NHL (-25.2)</t>
-  </si>
-  <si>
-    <t>AdersA.25ptethnicityunk</t>
-  </si>
-  <si>
-    <t>25_PtEthnicity_Unk (-25.3)</t>
-  </si>
-  <si>
-    <t>AdersA.25ptethnicityother</t>
-  </si>
-  <si>
-    <t>25_PtEthnicity_Other (-25.4)</t>
-  </si>
-  <si>
-    <t>AdersA.0pticnfull</t>
-  </si>
-  <si>
-    <t>0_Pt_ICN_Full (-0)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac1typebrand</t>
-  </si>
-  <si>
-    <t>17_Vac1_TypeBrand (-17.11)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac1route</t>
-  </si>
-  <si>
-    <t>17_Vac1_Route (-17.12)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac1mfgr</t>
-  </si>
-  <si>
-    <t>17_Vac1_Mfgr (-17.13)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac1lot</t>
-  </si>
-  <si>
-    <t>17_Vac1_Lot (-17.14)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac1site</t>
-  </si>
-  <si>
-    <t>17_Vac1_Site (-17.15)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac1doseinseries</t>
-  </si>
-  <si>
-    <t>17_Vac1_DoseInSeries (-17.16)</t>
-  </si>
-  <si>
-    <t>AdersA.18vaedesc</t>
-  </si>
-  <si>
-    <t>18_VAE_Desc (-18)</t>
-  </si>
-  <si>
-    <t>AdersA.21vaeoutcomedrvisit</t>
-  </si>
-  <si>
-    <t>21_VAE_Outcome_DrVisit (-21.11)</t>
-  </si>
-  <si>
-    <t>AdersA.21vaeoutcomeered</t>
-  </si>
-  <si>
-    <t>21_VAE_Outcome_ErED (-21.12)</t>
-  </si>
-  <si>
-    <t>AdersA.21hospstay</t>
-  </si>
-  <si>
-    <t>21_HospStay (-21.21)</t>
-  </si>
-  <si>
-    <t>AdersA.21hospstaynumdays</t>
-  </si>
-  <si>
-    <t>21_HospStay_NumDays (-21.22)</t>
-  </si>
-  <si>
-    <t>AdersA.21hospstayname</t>
-  </si>
-  <si>
-    <t>21_HospStay_Name (-21.23)</t>
-  </si>
-  <si>
-    <t>AdersA.21hospstaycity</t>
-  </si>
-  <si>
-    <t>21_HospStay_City (-21.24)</t>
-  </si>
-  <si>
-    <t>AdersA.21hospstaystate</t>
-  </si>
-  <si>
-    <t>21_HospStay_State (-21.25)</t>
-  </si>
-  <si>
-    <t>AdersA.21prolonghospstay</t>
-  </si>
-  <si>
-    <t>21_ProlongHospStay (-21.3)</t>
-  </si>
-  <si>
-    <t>AdersA.21lti</t>
-  </si>
-  <si>
-    <t>21_LTI (-21.4)</t>
-  </si>
-  <si>
-    <t>AdersA.21dis</t>
-  </si>
-  <si>
-    <t>21_Dis (-21.5)</t>
-  </si>
-  <si>
-    <t>AdersA.21cabd</t>
-  </si>
-  <si>
-    <t>21_CA_BD (-21.8)</t>
-  </si>
-  <si>
-    <t>AdersA.21noa</t>
-  </si>
-  <si>
-    <t>21_NOA (-21.9)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac2typebrand</t>
-  </si>
-  <si>
-    <t>17_Vac2_TypeBrand (-17.21)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac2mfgr</t>
-  </si>
-  <si>
-    <t>17_Vac2_Mfgr (-17.22)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac2lot</t>
-  </si>
-  <si>
-    <t>17_Vac2_Lot (-17.23)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac2route</t>
-  </si>
-  <si>
-    <t>17_Vac2_Route (-17.24)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac2site</t>
-  </si>
-  <si>
-    <t>17_Vac2_Site (-17.25)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac2doseinseries</t>
-  </si>
-  <si>
-    <t>17_Vac2_DoseInSeries (-17.26)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac3typebrand</t>
-  </si>
-  <si>
-    <t>17_Vac3_TypeBrand (-17.31)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac3mfgr</t>
-  </si>
-  <si>
-    <t>17_Vac3_Mfgr (-17.32)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac3lot</t>
-  </si>
-  <si>
-    <t>17_Vac3_Lot (-17.33)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac3route</t>
-  </si>
-  <si>
-    <t>17_Vac3_Route (-17.34)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac3site</t>
-  </si>
-  <si>
-    <t>17_Vac3_Site (-17.35)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac3doseinseries</t>
-  </si>
-  <si>
-    <t>17_Vac3_DoseInSeries (-17.36)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac4typebrand</t>
-  </si>
-  <si>
-    <t>17_Vac4_TypeBrand (-17.41)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac4mfgr</t>
-  </si>
-  <si>
-    <t>17_Vac4_Mfgr (-17.42)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac4lot</t>
-  </si>
-  <si>
-    <t>17_Vac4_Lot (-17.43)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac4route</t>
-  </si>
-  <si>
-    <t>17_Vac4_Route (-17.44)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac4site</t>
-  </si>
-  <si>
-    <t>17_Vac4_Site (-17.45)</t>
-  </si>
-  <si>
-    <t>AdersA.17vac4doseinseries</t>
-  </si>
-  <si>
-    <t>17_Vac4_DoseInSeries (-17.46)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac1typebrand</t>
-  </si>
-  <si>
-    <t>22_PVac1_TypeBrand (-22.11)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac1mfgr</t>
-  </si>
-  <si>
-    <t>22_PVac1_Mfgr (-22.12)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac1lot</t>
-  </si>
-  <si>
-    <t>22_PVac1_Lot (-22.13)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac1route</t>
-  </si>
-  <si>
-    <t>22_PVac1_Route (-22.14)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac1site</t>
-  </si>
-  <si>
-    <t>22_PVac1_Site (-22.15)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac1doseinseries</t>
-  </si>
-  <si>
-    <t>22_PVac1_DoseInSeries (-22.16)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac1date</t>
-  </si>
-  <si>
-    <t>22_PVac1_Date (-22.17)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac2typebrand</t>
-  </si>
-  <si>
-    <t>22_PVac2_TypeBrand (-22.21)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac2mfgr</t>
-  </si>
-  <si>
-    <t>22_PVac2_Mfgr (-22.22)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac2lot</t>
-  </si>
-  <si>
-    <t>22_PVac2_Lot (-22.23)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac2route</t>
-  </si>
-  <si>
-    <t>22_PVac2_Route (-22.24)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac2site</t>
-  </si>
-  <si>
-    <t>22_PVac2_Site (-22.25)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac2doseinseries</t>
-  </si>
-  <si>
-    <t>22_PVac2_DoseInSeries (-22.26)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac2date</t>
-  </si>
-  <si>
-    <t>22_PVac2_Date (-22.27)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac3typebrand</t>
-  </si>
-  <si>
-    <t>22_PVac3_TypeBrand (-22.31)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac3mfgr</t>
-  </si>
-  <si>
-    <t>22_PVac3_Mfgr (-22.32)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac3lot</t>
-  </si>
-  <si>
-    <t>22_PVac3_Lot (-22.33)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac3route</t>
-  </si>
-  <si>
-    <t>22_PVac3_Route (-22.34)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac3site</t>
-  </si>
-  <si>
-    <t>22_PVac3_Site (-22.35)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac3doseinseries</t>
-  </si>
-  <si>
-    <t>22_PVac3_DoseInSeries (-22.36)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac3date</t>
-  </si>
-  <si>
-    <t>22_PVac3_Date (-22.37)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac4typebrand</t>
-  </si>
-  <si>
-    <t>22_PVac4_TypeBrand (-22.41)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac4mfgr</t>
-  </si>
-  <si>
-    <t>22_PVac4_Mfgr (-22.42)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac4lot</t>
-  </si>
-  <si>
-    <t>22_PVac4_Lot (-22.43)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac4route</t>
-  </si>
-  <si>
-    <t>22_PVac4_Route (-22.44)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac4site</t>
-  </si>
-  <si>
-    <t>22_PVac4_Site (-22.45)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac4doseinseries</t>
-  </si>
-  <si>
-    <t>22_PVac4_DoseInSeries (-22.46)</t>
-  </si>
-  <si>
-    <t>AdersA.22pvac4date</t>
-  </si>
-  <si>
-    <t>22_PVac4_Date (-22.47)</t>
+    <t>Pt_ICN_Full (-0)</t>
+  </si>
+  <si>
+    <t>AdersA.ptdob</t>
+  </si>
+  <si>
+    <t>ptDOB (-2)</t>
+  </si>
+  <si>
+    <t>AdersA.ptsex</t>
+  </si>
+  <si>
+    <t>ptSex (-3)</t>
+  </si>
+  <si>
+    <t>AdersA.death</t>
+  </si>
+  <si>
+    <t>Death (-21.6)</t>
+  </si>
+  <si>
+    <t>AdersA.deathdt</t>
+  </si>
+  <si>
+    <t>DeathDt (-21.7)</t>
+  </si>
+  <si>
+    <t>AdersA.ptraceaian</t>
+  </si>
+  <si>
+    <t>PtRace_AIAN (-24.1)</t>
+  </si>
+  <si>
+    <t>AdersA.ptraceasian</t>
+  </si>
+  <si>
+    <t>PtRace_Asian (-24.2)</t>
+  </si>
+  <si>
+    <t>AdersA.ptraceblkam</t>
+  </si>
+  <si>
+    <t>PtRace_BlkAM (-24.3)</t>
+  </si>
+  <si>
+    <t>AdersA.ptracenhopi</t>
+  </si>
+  <si>
+    <t>PtRace_NH_OPI (-24.4)</t>
+  </si>
+  <si>
+    <t>AdersA.ptracewhite</t>
+  </si>
+  <si>
+    <t>PtRace_White (-24.5)</t>
+  </si>
+  <si>
+    <t>AdersA.ptraceunk</t>
+  </si>
+  <si>
+    <t>PtRace_Unk (-24.6)</t>
+  </si>
+  <si>
+    <t>AdersA.ptraceother</t>
+  </si>
+  <si>
+    <t>PtRace_Other (-24.7)</t>
+  </si>
+  <si>
+    <t>AdersA.ptethnicityhisplat</t>
+  </si>
+  <si>
+    <t>PtEthnicity_HispLat (-25.1)</t>
+  </si>
+  <si>
+    <t>AdersA.ptethnicitynhl</t>
+  </si>
+  <si>
+    <t>PtEthnicity_NHL (-25.2)</t>
+  </si>
+  <si>
+    <t>AdersA.ptethnicityunk</t>
+  </si>
+  <si>
+    <t>PtEthnicity_Unk (-25.3)</t>
+  </si>
+  <si>
+    <t>AdersA.ptethnicityother</t>
+  </si>
+  <si>
+    <t>PtEthnicity_Other (-25.4)</t>
+  </si>
+  <si>
+    <t>AdersA.vac1typebrand</t>
+  </si>
+  <si>
+    <t>Vac1_TypeBrand (-17.11)</t>
+  </si>
+  <si>
+    <t>AdersA.vac1mfgr</t>
+  </si>
+  <si>
+    <t>Vac1_Mfgr (-17.13)</t>
+  </si>
+  <si>
+    <t>AdersA.vac1lot</t>
+  </si>
+  <si>
+    <t>Vac1_Lot (-17.14)</t>
+  </si>
+  <si>
+    <t>AdersA.vac1site</t>
+  </si>
+  <si>
+    <t>Vac1_Site (-17.15)</t>
+  </si>
+  <si>
+    <t>AdersA.vac1doseinseries</t>
+  </si>
+  <si>
+    <t>Vac1_DoseInSeries (-17.16)</t>
+  </si>
+  <si>
+    <t>AdersA.vaedesc</t>
+  </si>
+  <si>
+    <t>VAE_Desc (-18)</t>
+  </si>
+  <si>
+    <t>AdersA.vaeoutcomedrvisit</t>
+  </si>
+  <si>
+    <t>VAE_Outcome_DrVisit (-21.11)</t>
+  </si>
+  <si>
+    <t>AdersA.vaeoutcomeered</t>
+  </si>
+  <si>
+    <t>VAE_Outcome_ErED (-21.12)</t>
+  </si>
+  <si>
+    <t>AdersA.hospstay</t>
+  </si>
+  <si>
+    <t>HospStay (-21.21)</t>
+  </si>
+  <si>
+    <t>AdersA.hospstaynumdays</t>
+  </si>
+  <si>
+    <t>HospStay_NumDays (-21.22)</t>
+  </si>
+  <si>
+    <t>AdersA.hospstayname</t>
+  </si>
+  <si>
+    <t>HospStay_Name (-21.23)</t>
+  </si>
+  <si>
+    <t>AdersA.hospstaycity</t>
+  </si>
+  <si>
+    <t>HospStay_City (-21.24)</t>
+  </si>
+  <si>
+    <t>AdersA.hospstaystate</t>
+  </si>
+  <si>
+    <t>HospStay_State (-21.25)</t>
+  </si>
+  <si>
+    <t>AdersA.prolonghospstay</t>
+  </si>
+  <si>
+    <t>ProlongHospStay (-21.3)</t>
+  </si>
+  <si>
+    <t>AdersA.lti</t>
+  </si>
+  <si>
+    <t>LTI (-21.4)</t>
+  </si>
+  <si>
+    <t>AdersA.dis</t>
+  </si>
+  <si>
+    <t>Dis (-21.5)</t>
+  </si>
+  <si>
+    <t>AdersA.cabd</t>
+  </si>
+  <si>
+    <t>CA_BD (-21.8)</t>
+  </si>
+  <si>
+    <t>AdersA.noa</t>
+  </si>
+  <si>
+    <t>NOA (-21.9)</t>
+  </si>
+  <si>
+    <t>AdersA.vac2typebrand</t>
+  </si>
+  <si>
+    <t>Vac2_TypeBrand (-17.21)</t>
+  </si>
+  <si>
+    <t>AdersA.vac2mfgr</t>
+  </si>
+  <si>
+    <t>Vac2_Mfgr (-17.22)</t>
+  </si>
+  <si>
+    <t>AdersA.vac2lot</t>
+  </si>
+  <si>
+    <t>Vac2_Lot (-17.23)</t>
+  </si>
+  <si>
+    <t>AdersA.vac2route</t>
+  </si>
+  <si>
+    <t>Vac2_Route (-17.24)</t>
+  </si>
+  <si>
+    <t>AdersA.vac2site</t>
+  </si>
+  <si>
+    <t>Vac2_Site (-17.25)</t>
+  </si>
+  <si>
+    <t>AdersA.vac2doseinseries</t>
+  </si>
+  <si>
+    <t>Vac2_DoseInSeries (-17.26)</t>
+  </si>
+  <si>
+    <t>AdersA.vac3typebrand</t>
+  </si>
+  <si>
+    <t>Vac3_TypeBrand (-17.31)</t>
+  </si>
+  <si>
+    <t>AdersA.vac3mfgr</t>
+  </si>
+  <si>
+    <t>Vac3_Mfgr (-17.32)</t>
+  </si>
+  <si>
+    <t>AdersA.vac3lot</t>
+  </si>
+  <si>
+    <t>Vac3_Lot (-17.33)</t>
+  </si>
+  <si>
+    <t>AdersA.vac3route</t>
+  </si>
+  <si>
+    <t>Vac3_Route (-17.34)</t>
+  </si>
+  <si>
+    <t>AdersA.vac3site</t>
+  </si>
+  <si>
+    <t>Vac3_Site (-17.35)</t>
+  </si>
+  <si>
+    <t>AdersA.vac3doseinseries</t>
+  </si>
+  <si>
+    <t>Vac3_DoseInSeries (-17.36)</t>
+  </si>
+  <si>
+    <t>AdersA.vac4typebrand</t>
+  </si>
+  <si>
+    <t>Vac4_TypeBrand (-17.41)</t>
+  </si>
+  <si>
+    <t>AdersA.vac4mfgr</t>
+  </si>
+  <si>
+    <t>Vac4_Mfgr (-17.42)</t>
+  </si>
+  <si>
+    <t>AdersA.vac4lot</t>
+  </si>
+  <si>
+    <t>Vac4_Lot (-17.43)</t>
+  </si>
+  <si>
+    <t>AdersA.vac4route</t>
+  </si>
+  <si>
+    <t>Vac4_Route (-17.44)</t>
+  </si>
+  <si>
+    <t>AdersA.vac4site</t>
+  </si>
+  <si>
+    <t>Vac4_Site (-17.45)</t>
+  </si>
+  <si>
+    <t>AdersA.vac4doseinseries</t>
+  </si>
+  <si>
+    <t>Vac4_DoseInSeries (-17.46)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac1typebrand</t>
+  </si>
+  <si>
+    <t>PVac1_TypeBrand (-22.11)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac1mfgr</t>
+  </si>
+  <si>
+    <t>PVac1_Mfgr (-22.12)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac1lot</t>
+  </si>
+  <si>
+    <t>PVac1_Lot (-22.13)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac1route</t>
+  </si>
+  <si>
+    <t>PVac1_Route (-22.14)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac1site</t>
+  </si>
+  <si>
+    <t>PVac1_Site (-22.15)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac1doseinseries</t>
+  </si>
+  <si>
+    <t>PVac1_DoseInSeries (-22.16)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac1date</t>
+  </si>
+  <si>
+    <t>PVac1_Date (-22.17)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac2typebrand</t>
+  </si>
+  <si>
+    <t>PVac2_TypeBrand (-22.21)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac2mfgr</t>
+  </si>
+  <si>
+    <t>PVac2_Mfgr (-22.22)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac2lot</t>
+  </si>
+  <si>
+    <t>PVac2_Lot (-22.23)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac2route</t>
+  </si>
+  <si>
+    <t>PVac2_Route (-22.24)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac2site</t>
+  </si>
+  <si>
+    <t>PVac2_Site (-22.25)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac2doseinseries</t>
+  </si>
+  <si>
+    <t>PVac2_DoseInSeries (-22.26)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac2date</t>
+  </si>
+  <si>
+    <t>PVac2_Date (-22.27)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac3typebrand</t>
+  </si>
+  <si>
+    <t>PVac3_TypeBrand (-22.31)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac3mfgr</t>
+  </si>
+  <si>
+    <t>PVac3_Mfgr (-22.32)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac3lot</t>
+  </si>
+  <si>
+    <t>PVac3_Lot (-22.33)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac3route</t>
+  </si>
+  <si>
+    <t>PVac3_Route (-22.34)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac3site</t>
+  </si>
+  <si>
+    <t>PVac3_Site (-22.35)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac3doseinseries</t>
+  </si>
+  <si>
+    <t>PVac3_DoseInSeries (-22.36)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac3date</t>
+  </si>
+  <si>
+    <t>PVac3_Date (-22.37)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac4typebrand</t>
+  </si>
+  <si>
+    <t>PVac4_TypeBrand (-22.41)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac4mfgr</t>
+  </si>
+  <si>
+    <t>PVac4_Mfgr (-22.42)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac4lot</t>
+  </si>
+  <si>
+    <t>PVac4_Lot (-22.43)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac4route</t>
+  </si>
+  <si>
+    <t>PVac4_Route (-22.44)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac4site</t>
+  </si>
+  <si>
+    <t>PVac4_Site (-22.45)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac4doseinseries</t>
+  </si>
+  <si>
+    <t>PVac4_DoseInSeries (-22.46)</t>
+  </si>
+  <si>
+    <t>AdersA.pvac4date</t>
+  </si>
+  <si>
+    <t>PVac4_Date (-22.47)</t>
   </si>
 </sst>
 </file>
@@ -1039,11 +1033,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ83"/>
+  <dimension ref="A1:AJ82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="27.546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="25.21484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.21484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -1073,7 +1067,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="27.546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="25.21484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -9289,106 +9283,6 @@
         <v>72</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
